--- a/code/python/functions/bid_list/bid_lists/Secondary List 9.8.26.xlsx
+++ b/code/python/functions/bid_list/bid_lists/Secondary List 9.8.26.xlsx
@@ -1,45 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30522"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nucor-my.sharepoint.com/personal/alex_holifield_nucor_com/Documents/Documents/Secondary Market/2026 Week 36/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{5502F7E4-BA2B-40CD-ACFC-3B2589C30BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32509266-1A65-487A-A3D3-E8EDCCE0ECD4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Excess And Secondary Sales List" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" name="Excess And Secondary Sales List" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Excess And Secondary Sales List'!$A$1:$AT$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Excess And Secondary Sales List'!$A$1:$AT$45</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="176">
   <si>
     <t>Bids</t>
   </si>
@@ -882,24 +881,29 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0000;\-0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000;\-0.000"/>
+    <numFmt numFmtId="2023" formatCode="0.0000;\-0.0000"/>
+    <numFmt numFmtId="2024" formatCode="0.000;\-0.000"/>
   </numFmts>
   <fonts count="3">
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <i val="0"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -915,13 +919,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF007D00"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -949,53 +951,68 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="2023" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="2024" fontId="1" fillId="2" borderId="1" xfId="0">
+      <alignment horizontal="right" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+  <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1041,7 +1058,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1093,7 +1110,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1154,187 +1171,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xr:uid="{27181609-1D1A-4717-9576-54ACDF08F23C}" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AT45"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="12.75" defaultColWidth="9.140625" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="9" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" style="9" customWidth="1"/>
-    <col min="8" max="12" width="10.7109375" style="9" customWidth="1"/>
-    <col min="13" max="13" width="26.7109375" style="9" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="9" customWidth="1"/>
-    <col min="15" max="15" width="23.42578125" style="9" customWidth="1"/>
-    <col min="16" max="16" width="66.42578125" style="9" customWidth="1"/>
-    <col min="17" max="46" width="10.7109375" style="9" customWidth="1"/>
-    <col min="47" max="47" width="4.7109375" style="9" customWidth="1"/>
-    <col min="48" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="2" style="9" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" style="9" width="19.28125" customWidth="1"/>
+    <col min="4" max="4" style="9" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" style="9" width="16.57421875" customWidth="1"/>
+    <col min="6" max="6" style="9" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" style="9" width="18.8515625" customWidth="1"/>
+    <col min="8" max="12" style="9" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" style="9" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" style="9" width="10.7109375" customWidth="1"/>
+    <col min="15" max="15" style="9" width="23.421875" customWidth="1"/>
+    <col min="16" max="16" style="9" width="66.421875" customWidth="1"/>
+    <col min="17" max="46" style="9" width="10.7109375" customWidth="1"/>
+    <col min="47" max="47" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="3" customFormat="1" ht="27.75" customHeight="1">
+    <row r="1" ht="27.75" customHeight="1" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1474,57 +1494,57 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+    <row r="2" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="5">
-        <v>2183055.2000000002</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="4">
+        <v>2183055.2</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>14934</v>
       </c>
-      <c r="J2" s="6">
-        <v>7.4669999999999996</v>
-      </c>
-      <c r="K2" s="5">
-        <v>2.3E-2</v>
-      </c>
-      <c r="L2" s="5">
-        <v>48.116100000000003</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="J2" s="5">
+        <v>7.467</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.023</v>
+      </c>
+      <c r="L2" s="4">
+        <v>48.1161</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="Q2" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="R2" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S2" s="7">
@@ -1549,120 +1569,120 @@
         <v>0</v>
       </c>
       <c r="Z2" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AA2" s="8">
         <v>0.12</v>
       </c>
       <c r="AB2" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC2" s="8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AD2" s="8">
-        <v>2.1000000000000001E-2</v>
+        <v>0.021</v>
       </c>
       <c r="AE2" s="8">
         <v>0.115</v>
       </c>
       <c r="AF2" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG2" s="8">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AH2" s="8">
         <v>0.01</v>
       </c>
       <c r="AI2" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ2" s="8">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AK2" s="8">
         <v>0</v>
       </c>
       <c r="AL2" s="8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AM2" s="8">
         <v>0</v>
       </c>
       <c r="AN2" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO2" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP2" s="8">
-        <v>4.7000000000000002E-3</v>
+        <v>0.0047</v>
       </c>
       <c r="AQ2" s="8">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="AR2" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS2" s="4" t="s">
+        <v>0.0064</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS2" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT2" s="4" t="s">
+      <c r="AT2" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+    <row r="3" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>2193815.1</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>26590</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>13.295</v>
       </c>
-      <c r="K3" s="5">
-        <v>5.9400000000000001E-2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>60.142499999999998</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="K3" s="4">
+        <v>0.0594</v>
+      </c>
+      <c r="L3" s="4">
+        <v>60.1425</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S3" s="7">
@@ -1687,120 +1707,120 @@
         <v>0</v>
       </c>
       <c r="Z3" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AA3" s="8">
-        <v>0.14699999999999999</v>
+        <v>0.147</v>
       </c>
       <c r="AB3" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC3" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD3" s="8">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="AE3" s="8">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AF3" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AG3" s="8">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="AH3" s="8">
         <v>0.01</v>
       </c>
       <c r="AI3" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ3" s="8">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AK3" s="8">
         <v>0</v>
       </c>
       <c r="AL3" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AM3" s="8">
         <v>0</v>
       </c>
       <c r="AN3" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO3" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP3" s="8">
         <v>0</v>
       </c>
       <c r="AQ3" s="8">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="AR3" s="4" t="s">
+        <v>0.0071</v>
+      </c>
+      <c r="AR3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS3" s="4" t="s">
+      <c r="AS3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT3" s="4" t="s">
+      <c r="AT3" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+    <row r="4" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>2193012.1</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>21860</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>10.93</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>0.1027</v>
       </c>
-      <c r="L4" s="5">
-        <v>60.145899999999997</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="L4" s="4">
+        <v>60.1459</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S4" s="7">
@@ -1828,117 +1848,117 @@
         <v>0.03</v>
       </c>
       <c r="AA4" s="8">
-        <v>0.13600000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="AB4" s="8">
         <v>0.01</v>
       </c>
       <c r="AC4" s="8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AD4" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AE4" s="8">
-        <v>0.11600000000000001</v>
+        <v>0.116</v>
       </c>
       <c r="AF4" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG4" s="8">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AH4" s="8">
         <v>0.01</v>
       </c>
       <c r="AI4" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ4" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AK4" s="8">
         <v>0</v>
       </c>
       <c r="AL4" s="8">
-        <v>3.2000000000000002E-3</v>
+        <v>0.0032</v>
       </c>
       <c r="AM4" s="8">
         <v>0</v>
       </c>
       <c r="AN4" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO4" s="8">
-        <v>2.8999999999999998E-3</v>
+        <v>0.0029</v>
       </c>
       <c r="AP4" s="8">
         <v>0</v>
       </c>
       <c r="AQ4" s="8">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="AR4" s="4" t="s">
+        <v>0.0069</v>
+      </c>
+      <c r="AR4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS4" s="4" t="s">
+      <c r="AS4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AT4" s="4" t="s">
+      <c r="AT4" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4" t="s">
+    <row r="5" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>2191422.1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>21380</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>10.69</v>
       </c>
-      <c r="K5" s="5">
-        <v>4.9099999999999998E-2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>48.011899999999997</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="K5" s="4">
+        <v>0.0491</v>
+      </c>
+      <c r="L5" s="4">
+        <v>48.0119</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S5" s="7">
@@ -1963,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="8">
-        <v>2.1000000000000001E-2</v>
+        <v>0.021</v>
       </c>
       <c r="AA5" s="8">
         <v>0.126</v>
@@ -1972,118 +1992,118 @@
         <v>0.01</v>
       </c>
       <c r="AC5" s="8">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AD5" s="8">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="AE5" s="8">
-        <v>8.3000000000000004E-2</v>
+        <v>0.083</v>
       </c>
       <c r="AF5" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG5" s="8">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AH5" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI5" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ5" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AK5" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL5" s="8">
-        <v>3.7000000000000002E-3</v>
+        <v>0.0037</v>
       </c>
       <c r="AM5" s="8">
         <v>0</v>
       </c>
       <c r="AN5" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO5" s="8">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AP5" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ5" s="8">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AR5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS5" s="4" t="s">
+        <v>0.007</v>
+      </c>
+      <c r="AR5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AT5" s="4" t="s">
+      <c r="AT5" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+    <row r="6" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>2177061.1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>22380</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>11.19</v>
       </c>
-      <c r="K6" s="5">
-        <v>5.6599999999999998E-2</v>
-      </c>
-      <c r="L6" s="5">
-        <v>58.684899999999999</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="K6" s="4">
+        <v>0.0566</v>
+      </c>
+      <c r="L6" s="4">
+        <v>58.6849</v>
+      </c>
+      <c r="M6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="N6" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S6" s="7">
         <v>56.4</v>
       </c>
       <c r="T6" s="7">
-        <v>80.400000000000006</v>
+        <v>80.4</v>
       </c>
       <c r="U6" s="7">
         <v>27</v>
@@ -2107,114 +2127,114 @@
         <v>0.495</v>
       </c>
       <c r="AB6" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC6" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD6" s="8">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE6" s="8">
-        <v>7.5999999999999998E-2</v>
+        <v>0.076</v>
       </c>
       <c r="AF6" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG6" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AH6" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI6" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ6" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK6" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL6" s="8">
         <v>0</v>
       </c>
       <c r="AM6" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN6" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO6" s="8">
-        <v>1.6999999999999999E-3</v>
+        <v>0.0017</v>
       </c>
       <c r="AP6" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ6" s="8">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="AR6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS6" s="4" t="s">
+        <v>0.008</v>
+      </c>
+      <c r="AR6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AT6" s="4" t="s">
+      <c r="AT6" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4" t="s">
+    <row r="7" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>2187063.1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>22440</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>11.22</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="4">
         <v>0.1018</v>
       </c>
-      <c r="L7" s="5">
-        <v>48.133600000000001</v>
-      </c>
-      <c r="M7" s="4" t="s">
+      <c r="L7" s="4">
+        <v>48.1336</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S7" s="7">
@@ -2239,120 +2259,120 @@
         <v>0</v>
       </c>
       <c r="Z7" s="8">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="AA7" s="8">
         <v>0.318</v>
       </c>
       <c r="AB7" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC7" s="8">
-        <v>1.1999999999999999E-3</v>
+        <v>0.0012</v>
       </c>
       <c r="AD7" s="8">
         <v>0.02</v>
       </c>
       <c r="AE7" s="8">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF7" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG7" s="8">
         <v>0.04</v>
       </c>
       <c r="AH7" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI7" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ7" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AK7" s="8">
         <v>0</v>
       </c>
       <c r="AL7" s="8">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AM7" s="8">
         <v>0</v>
       </c>
       <c r="AN7" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO7" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AP7" s="8">
         <v>0</v>
       </c>
       <c r="AQ7" s="8">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="AR7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS7" s="4" t="s">
+        <v>0.0061</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AT7" s="4" t="s">
+      <c r="AT7" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4" t="s">
+    <row r="8" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>2181762</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>40510</v>
       </c>
-      <c r="J8" s="6">
-        <v>20.254999999999999</v>
-      </c>
-      <c r="K8" s="5">
-        <v>1.95E-2</v>
-      </c>
-      <c r="L8" s="5">
+      <c r="J8" s="5">
+        <v>20.255</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.0195</v>
+      </c>
+      <c r="L8" s="4">
         <v>42.8125</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="N8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="R8" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S8" s="7">
@@ -2377,114 +2397,114 @@
         <v>0</v>
       </c>
       <c r="Z8" s="8">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AA8" s="8">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="AB8" s="8">
         <v>0.01</v>
       </c>
       <c r="AC8" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AD8" s="8">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="AE8" s="8">
-        <v>0.11700000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="AF8" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AG8" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH8" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI8" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ8" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK8" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL8" s="8">
-        <v>4.0000000000000002E-4</v>
+        <v>0.0004</v>
       </c>
       <c r="AM8" s="8">
         <v>0</v>
       </c>
       <c r="AN8" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO8" s="8">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AP8" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ8" s="8">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AR8" s="4" t="s">
+        <v>0.005</v>
+      </c>
+      <c r="AR8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS8" s="4" t="s">
+      <c r="AS8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT8" s="4" t="s">
+      <c r="AT8" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:46" s="3" customFormat="1" ht="52.35" customHeight="1">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4" t="s">
+    <row r="9" ht="52.5" customHeight="1" s="1" customFormat="1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>2042246</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>13250</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>6.625</v>
       </c>
-      <c r="K9" s="5">
-        <v>2.4899999999999999E-2</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="K9" s="4">
+        <v>0.0249</v>
+      </c>
+      <c r="L9" s="4">
         <v>60.1875</v>
       </c>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4" t="s">
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="P9" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4" t="s">
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S9" s="7">
@@ -2509,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AA9" s="8">
         <v>0.121</v>
@@ -2518,111 +2538,111 @@
         <v>0.01</v>
       </c>
       <c r="AC9" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AD9" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AE9" s="8">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="AF9" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG9" s="8">
         <v>0.04</v>
       </c>
       <c r="AH9" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI9" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ9" s="8">
         <v>0.04</v>
       </c>
       <c r="AK9" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL9" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AM9" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN9" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO9" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AP9" s="8">
-        <v>2.9999999999999997E-4</v>
+        <v>0.0003</v>
       </c>
       <c r="AQ9" s="8">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="AR9" s="4" t="s">
+        <v>0.0061</v>
+      </c>
+      <c r="AR9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS9" s="4" t="s">
+      <c r="AS9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT9" s="4" t="s">
+      <c r="AT9" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4" t="s">
+    <row r="10" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="5">
-        <v>2179037.2000000002</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" s="4">
+        <v>2179037.2</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>10332</v>
       </c>
-      <c r="J10" s="6">
-        <v>5.1660000000000004</v>
-      </c>
-      <c r="K10" s="5">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="L10" s="5">
+      <c r="J10" s="5">
+        <v>5.166</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.044</v>
+      </c>
+      <c r="L10" s="4">
         <v>60.1875</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="P10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="Q10" s="4" t="s">
+      <c r="Q10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="R10" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S10" s="7">
@@ -2647,127 +2667,127 @@
         <v>0</v>
       </c>
       <c r="Z10" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AA10" s="8">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="AB10" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC10" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AD10" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AE10" s="8">
-        <v>0.10100000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="AF10" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG10" s="8">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH10" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AI10" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ10" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AK10" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL10" s="8">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AM10" s="8">
         <v>0</v>
       </c>
       <c r="AN10" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO10" s="8">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AP10" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ10" s="8">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="AR10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS10" s="4" t="s">
+        <v>0.0071</v>
+      </c>
+      <c r="AR10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS10" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT10" s="4" t="s">
+      <c r="AT10" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+    <row r="11" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>2166151</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>41910</v>
       </c>
-      <c r="J11" s="6">
-        <v>20.954999999999998</v>
-      </c>
-      <c r="K11" s="5">
-        <v>4.8099999999999997E-2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>49.613399999999999</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="J11" s="5">
+        <v>20.955</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.0481</v>
+      </c>
+      <c r="L11" s="4">
+        <v>49.6134</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="N11" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="O11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="P11" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="Q11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="R11" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S11" s="7">
         <v>65.8</v>
       </c>
       <c r="T11" s="7">
-        <v>81.599999999999994</v>
+        <v>81.6</v>
       </c>
       <c r="U11" s="7">
         <v>26</v>
@@ -2788,122 +2808,122 @@
         <v>0.22</v>
       </c>
       <c r="AA11" s="8">
-        <v>0.50700000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="AB11" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC11" s="8">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD11" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AE11" s="8">
-        <v>0.13700000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="AF11" s="8">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AG11" s="8">
-        <v>7.4999999999999997E-2</v>
+        <v>0.075</v>
       </c>
       <c r="AH11" s="8">
-        <v>1.6E-2</v>
+        <v>0.016</v>
       </c>
       <c r="AI11" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ11" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AK11" s="8">
         <v>0</v>
       </c>
       <c r="AL11" s="8">
-        <v>6.9999999999999999E-4</v>
+        <v>0.0007</v>
       </c>
       <c r="AM11" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN11" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO11" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP11" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ11" s="8">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="AR11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS11" s="4" t="s">
+        <v>0.0075</v>
+      </c>
+      <c r="AR11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AT11" s="4" t="s">
+      <c r="AT11" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:46" s="3" customFormat="1" ht="116.85" customHeight="1">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4" t="s">
+    <row r="12" ht="117" customHeight="1" s="1" customFormat="1">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>2176918</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>40152</v>
       </c>
-      <c r="J12" s="6">
-        <v>20.076000000000001</v>
-      </c>
-      <c r="K12" s="5">
-        <v>5.5300000000000002E-2</v>
-      </c>
-      <c r="L12" s="5">
-        <v>51.353999999999999</v>
-      </c>
-      <c r="M12" s="4" t="s">
+      <c r="J12" s="5">
+        <v>20.076</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.0553</v>
+      </c>
+      <c r="L12" s="4">
+        <v>51.354</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4" t="s">
+      <c r="N12" s="3"/>
+      <c r="O12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="P12" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Q12" s="4" t="s">
+      <c r="Q12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="R12" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S12" s="7">
         <v>52.4</v>
       </c>
       <c r="T12" s="7">
-        <v>64.400000000000006</v>
+        <v>64.4</v>
       </c>
       <c r="U12" s="7">
         <v>32</v>
@@ -2921,120 +2941,120 @@
         <v>0</v>
       </c>
       <c r="Z12" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AA12" s="8">
-        <v>0.57599999999999996</v>
+        <v>0.576</v>
       </c>
       <c r="AB12" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC12" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AD12" s="8">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE12" s="8">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="AF12" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG12" s="8">
-        <v>4.3999999999999997E-2</v>
+        <v>0.044</v>
       </c>
       <c r="AH12" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI12" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ12" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AK12" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL12" s="8">
-        <v>2.06E-2</v>
+        <v>0.0206</v>
       </c>
       <c r="AM12" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN12" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO12" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AP12" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ12" s="8">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="AR12" s="4" t="s">
+        <v>0.0075</v>
+      </c>
+      <c r="AR12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS12" s="4" t="s">
+      <c r="AS12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT12" s="4" t="s">
+      <c r="AT12" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
+    <row r="13" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>2185762.21</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>10749</v>
       </c>
-      <c r="J13" s="6">
-        <v>5.3745000000000003</v>
-      </c>
-      <c r="K13" s="5">
-        <v>5.74E-2</v>
-      </c>
-      <c r="L13" s="5">
+      <c r="J13" s="5">
+        <v>5.3745</v>
+      </c>
+      <c r="K13" s="4">
+        <v>0.0574</v>
+      </c>
+      <c r="L13" s="4">
         <v>54.1875</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N13" s="4" t="s">
+      <c r="N13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="P13" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="Q13" s="4" t="s">
+      <c r="Q13" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="R13" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S13" s="7">
@@ -3059,120 +3079,120 @@
         <v>0</v>
       </c>
       <c r="Z13" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AA13" s="8">
         <v>0.122</v>
       </c>
       <c r="AB13" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AC13" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AD13" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AE13" s="8">
-        <v>8.8999999999999996E-2</v>
+        <v>0.089</v>
       </c>
       <c r="AF13" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG13" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AH13" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI13" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ13" s="8">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AK13" s="8">
         <v>0</v>
       </c>
       <c r="AL13" s="8">
-        <v>3.3999999999999998E-3</v>
+        <v>0.0034</v>
       </c>
       <c r="AM13" s="8">
         <v>0</v>
       </c>
       <c r="AN13" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO13" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AP13" s="8">
         <v>0</v>
       </c>
       <c r="AQ13" s="8">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="AR13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS13" s="4" t="s">
+        <v>0.0073</v>
+      </c>
+      <c r="AR13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS13" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT13" s="4" t="s">
+      <c r="AT13" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4" t="s">
+    <row r="14" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>2193928.21</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>15650</v>
       </c>
-      <c r="J14" s="6">
-        <v>7.8250000000000002</v>
-      </c>
-      <c r="K14" s="5">
-        <v>6.2899999999999998E-2</v>
-      </c>
-      <c r="L14" s="5">
-        <v>60.054600000000001</v>
-      </c>
-      <c r="M14" s="4" t="s">
+      <c r="J14" s="5">
+        <v>7.825</v>
+      </c>
+      <c r="K14" s="4">
+        <v>0.0629</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60.0546</v>
+      </c>
+      <c r="M14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="N14" s="4" t="s">
+      <c r="N14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="O14" s="4" t="s">
+      <c r="O14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="P14" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="Q14" s="4" t="s">
+      <c r="Q14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="R14" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S14" s="7">
@@ -3197,120 +3217,120 @@
         <v>0</v>
       </c>
       <c r="Z14" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AA14" s="8">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AB14" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC14" s="8">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD14" s="8">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AE14" s="8">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="AF14" s="8">
         <v>0.04</v>
       </c>
       <c r="AG14" s="8">
-        <v>5.8000000000000003E-2</v>
+        <v>0.058</v>
       </c>
       <c r="AH14" s="8">
         <v>0.01</v>
       </c>
       <c r="AI14" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ14" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AK14" s="8">
         <v>0</v>
       </c>
       <c r="AL14" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AM14" s="8">
         <v>0</v>
       </c>
       <c r="AN14" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO14" s="8">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AP14" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ14" s="8">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="AR14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS14" s="4" t="s">
+        <v>0.0057</v>
+      </c>
+      <c r="AR14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT14" s="4" t="s">
+      <c r="AT14" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="15" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4" t="s">
+    <row r="15" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>2133101.1</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>21010</v>
       </c>
-      <c r="J15" s="6">
-        <v>10.505000000000001</v>
-      </c>
-      <c r="K15" s="5">
-        <v>2.41E-2</v>
-      </c>
-      <c r="L15" s="5">
+      <c r="J15" s="5">
+        <v>10.505</v>
+      </c>
+      <c r="K15" s="4">
+        <v>0.0241</v>
+      </c>
+      <c r="L15" s="4">
         <v>48.125</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="N15" s="4" t="s">
+      <c r="N15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="O15" s="4" t="s">
+      <c r="O15" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="P15" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="R15" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S15" s="7">
@@ -3335,114 +3355,114 @@
         <v>0</v>
       </c>
       <c r="Z15" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AA15" s="8">
         <v>0.123</v>
       </c>
       <c r="AB15" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AC15" s="8">
-        <v>3.5999999999999999E-3</v>
+        <v>0.0036</v>
       </c>
       <c r="AD15" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AE15" s="8">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="AF15" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG15" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH15" s="8">
         <v>0.01</v>
       </c>
       <c r="AI15" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ15" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK15" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL15" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AM15" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN15" s="8">
         <v>0</v>
       </c>
       <c r="AO15" s="8">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AP15" s="8">
-        <v>5.1000000000000004E-3</v>
+        <v>0.0051</v>
       </c>
       <c r="AQ15" s="8">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="AR15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS15" s="4" t="s">
+        <v>0.0067</v>
+      </c>
+      <c r="AR15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT15" s="4" t="s">
+      <c r="AT15" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+    <row r="16" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>2195685</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>37760</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>18.88</v>
       </c>
-      <c r="K16" s="5">
-        <v>8.48E-2</v>
-      </c>
-      <c r="L16" s="5">
-        <v>48.091000000000001</v>
-      </c>
-      <c r="M16" s="4" t="s">
+      <c r="K16" s="4">
+        <v>0.0848</v>
+      </c>
+      <c r="L16" s="4">
+        <v>48.091</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1" t="s">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4" t="s">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S16" s="7">
@@ -3467,114 +3487,114 @@
         <v>0</v>
       </c>
       <c r="Z16" s="8">
-        <v>5.3999999999999999E-2</v>
+        <v>0.054</v>
       </c>
       <c r="AA16" s="8">
-        <v>1.3480000000000001</v>
+        <v>1.348</v>
       </c>
       <c r="AB16" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC16" s="8">
-        <v>1.6999999999999999E-3</v>
+        <v>0.0017</v>
       </c>
       <c r="AD16" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AE16" s="8">
         <v>0.09</v>
       </c>
       <c r="AF16" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG16" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AH16" s="8">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AI16" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ16" s="8">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AK16" s="8">
         <v>0.105</v>
       </c>
       <c r="AL16" s="8">
-        <v>3.3999999999999998E-3</v>
+        <v>0.0034</v>
       </c>
       <c r="AM16" s="8">
         <v>0</v>
       </c>
       <c r="AN16" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO16" s="8">
-        <v>2.8999999999999998E-3</v>
+        <v>0.0029</v>
       </c>
       <c r="AP16" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ16" s="8">
-        <v>1.8700000000000001E-2</v>
-      </c>
-      <c r="AR16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS16" s="4" t="s">
+        <v>0.0187</v>
+      </c>
+      <c r="AR16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT16" s="4" t="s">
+      <c r="AT16" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:46" s="3" customFormat="1" ht="116.85" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4" t="s">
+    <row r="17" ht="117" customHeight="1" s="1" customFormat="1">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>2195899</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>43280</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="5">
         <v>21.64</v>
       </c>
-      <c r="K17" s="5">
-        <v>8.48E-2</v>
-      </c>
-      <c r="L17" s="5">
-        <v>44.613999999999997</v>
-      </c>
-      <c r="M17" s="4" t="s">
+      <c r="K17" s="4">
+        <v>0.0848</v>
+      </c>
+      <c r="L17" s="4">
+        <v>44.614</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1" t="s">
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4" t="s">
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S17" s="7"/>
@@ -3585,114 +3605,114 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
       <c r="Z17" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AA17" s="8">
-        <v>0.56100000000000005</v>
+        <v>0.561</v>
       </c>
       <c r="AB17" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC17" s="8">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AD17" s="8">
-        <v>1.9E-2</v>
+        <v>0.019</v>
       </c>
       <c r="AE17" s="8">
-        <v>0.16200000000000001</v>
+        <v>0.162</v>
       </c>
       <c r="AF17" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG17" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AH17" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI17" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ17" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AK17" s="8">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="AL17" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AM17" s="8">
         <v>0</v>
       </c>
       <c r="AN17" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO17" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP17" s="8">
         <v>0</v>
       </c>
       <c r="AQ17" s="8">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="AR17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS17" s="4" t="s">
+        <v>0.0156</v>
+      </c>
+      <c r="AR17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT17" s="4" t="s">
+      <c r="AT17" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:46" s="3" customFormat="1" ht="159.94999999999999" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4" t="s">
+    <row r="18" ht="159.75" customHeight="1" s="1" customFormat="1">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>2194050</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>49800</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="5">
         <v>24.9</v>
       </c>
-      <c r="K18" s="5">
-        <v>8.9700000000000002E-2</v>
-      </c>
-      <c r="L18" s="5">
+      <c r="K18" s="4">
+        <v>0.0897</v>
+      </c>
+      <c r="L18" s="4">
         <v>57.82</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1" t="s">
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="4" t="s">
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S18" s="7"/>
@@ -3703,121 +3723,121 @@
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
       <c r="Z18" s="8">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="AA18" s="8">
-        <v>0.82599999999999996</v>
+        <v>0.826</v>
       </c>
       <c r="AB18" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC18" s="8">
-        <v>1.1999999999999999E-3</v>
+        <v>0.0012</v>
       </c>
       <c r="AD18" s="8">
         <v>0.02</v>
       </c>
       <c r="AE18" s="8">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="AF18" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG18" s="8">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="AH18" s="8">
         <v>0.01</v>
       </c>
       <c r="AI18" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ18" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AK18" s="8">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AL18" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AM18" s="8">
         <v>0</v>
       </c>
       <c r="AN18" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO18" s="8">
-        <v>1.4E-3</v>
+        <v>0.0014</v>
       </c>
       <c r="AP18" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ18" s="8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="AR18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS18" s="4" t="s">
+        <v>0.015</v>
+      </c>
+      <c r="AR18" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT18" s="4" t="s">
+      <c r="AT18" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:46" s="3" customFormat="1" ht="138.19999999999999" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4" t="s">
+    <row r="19" ht="138" customHeight="1" s="1" customFormat="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>2195803</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>43980</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <v>21.99</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="4">
         <v>0.1048</v>
       </c>
-      <c r="L19" s="5">
-        <v>51.491999999999997</v>
-      </c>
-      <c r="M19" s="4" t="s">
+      <c r="L19" s="4">
+        <v>51.492</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1" t="s">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="4" t="s">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S19" s="7">
         <v>55.7</v>
       </c>
       <c r="T19" s="7">
-        <v>67.900000000000006</v>
+        <v>67.9</v>
       </c>
       <c r="U19" s="7">
         <v>29</v>
@@ -3838,111 +3858,111 @@
         <v>0.05</v>
       </c>
       <c r="AA19" s="8">
-        <v>0.47799999999999998</v>
+        <v>0.478</v>
       </c>
       <c r="AB19" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC19" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD19" s="8">
-        <v>1.9E-2</v>
+        <v>0.019</v>
       </c>
       <c r="AE19" s="8">
-        <v>0.10299999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="AF19" s="8">
         <v>0.03</v>
       </c>
       <c r="AG19" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AH19" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI19" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ19" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AK19" s="8">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AL19" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AM19" s="8">
         <v>0</v>
       </c>
       <c r="AN19" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO19" s="8">
-        <v>2.8999999999999998E-3</v>
+        <v>0.0029</v>
       </c>
       <c r="AP19" s="8">
         <v>0</v>
       </c>
       <c r="AQ19" s="8">
-        <v>1.09E-2</v>
-      </c>
-      <c r="AR19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS19" s="4" t="s">
+        <v>0.0109</v>
+      </c>
+      <c r="AR19" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT19" s="4" t="s">
+      <c r="AT19" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:46" s="3" customFormat="1" ht="127.5" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4" t="s">
+    <row r="20" ht="127.5" customHeight="1" s="1" customFormat="1">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>2193355</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>46000</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="5">
         <v>23</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="4">
         <v>0.1099</v>
       </c>
-      <c r="L20" s="5">
-        <v>62.947000000000003</v>
-      </c>
-      <c r="M20" s="4" t="s">
+      <c r="L20" s="4">
+        <v>62.947</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1" t="s">
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4" t="s">
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S20" s="7"/>
@@ -3953,114 +3973,114 @@
       <c r="X20" s="7"/>
       <c r="Y20" s="7"/>
       <c r="Z20" s="8">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="AA20" s="8">
-        <v>0.34300000000000003</v>
+        <v>0.343</v>
       </c>
       <c r="AB20" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC20" s="8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AD20" s="8">
-        <v>0.56599999999999995</v>
+        <v>0.566</v>
       </c>
       <c r="AE20" s="8">
         <v>0.127</v>
       </c>
       <c r="AF20" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AG20" s="8">
-        <v>5.7000000000000002E-2</v>
+        <v>0.057</v>
       </c>
       <c r="AH20" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI20" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ20" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AK20" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL20" s="8">
-        <v>4.1999999999999997E-3</v>
+        <v>0.0042</v>
       </c>
       <c r="AM20" s="8">
         <v>0</v>
       </c>
       <c r="AN20" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO20" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP20" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ20" s="8">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="AR20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS20" s="4" t="s">
+        <v>0.0057</v>
+      </c>
+      <c r="AR20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT20" s="4" t="s">
+      <c r="AT20" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
+    <row r="21" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>2195595</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>39420</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="5">
         <v>19.71</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="4">
         <v>0.1201</v>
       </c>
-      <c r="L21" s="5">
-        <v>51.762999999999998</v>
-      </c>
-      <c r="M21" s="4" t="s">
+      <c r="L21" s="4">
+        <v>51.763</v>
+      </c>
+      <c r="M21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1" t="s">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4" t="s">
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S21" s="7">
@@ -4085,114 +4105,114 @@
         <v>0</v>
       </c>
       <c r="Z21" s="8">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="AA21" s="8">
         <v>1.268</v>
       </c>
       <c r="AB21" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AC21" s="8">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AD21" s="8">
-        <v>2.4E-2</v>
+        <v>0.024</v>
       </c>
       <c r="AE21" s="8">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AF21" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AG21" s="8">
-        <v>6.3E-2</v>
+        <v>0.063</v>
       </c>
       <c r="AH21" s="8">
         <v>0.01</v>
       </c>
       <c r="AI21" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ21" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK21" s="8">
         <v>0.1</v>
       </c>
       <c r="AL21" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AM21" s="8">
         <v>0</v>
       </c>
       <c r="AN21" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO21" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP21" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ21" s="8">
-        <v>1.5800000000000002E-2</v>
-      </c>
-      <c r="AR21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS21" s="4" t="s">
+        <v>0.0158</v>
+      </c>
+      <c r="AR21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT21" s="4" t="s">
+      <c r="AT21" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4" t="s">
+    <row r="22" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>2188282</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>51610</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="5">
         <v>25.805</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="4">
         <v>0.125</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="4">
         <v>61.125</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1" t="s">
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4" t="s">
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S22" s="7"/>
@@ -4203,114 +4223,114 @@
       <c r="X22" s="7"/>
       <c r="Y22" s="7"/>
       <c r="Z22" s="8">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="AA22" s="8">
-        <v>0.34300000000000003</v>
+        <v>0.343</v>
       </c>
       <c r="AB22" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC22" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AD22" s="8">
-        <v>0.58899999999999997</v>
+        <v>0.589</v>
       </c>
       <c r="AE22" s="8">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="AF22" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AG22" s="8">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="AH22" s="8">
         <v>0.01</v>
       </c>
       <c r="AI22" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ22" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AK22" s="8">
         <v>0</v>
       </c>
       <c r="AL22" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AM22" s="8">
         <v>0</v>
       </c>
       <c r="AN22" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO22" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP22" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ22" s="8">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="AR22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS22" s="4" t="s">
+        <v>0.0073</v>
+      </c>
+      <c r="AR22" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS22" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT22" s="4" t="s">
+      <c r="AT22" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4" t="s">
+    <row r="23" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>2195855</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>47720</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <v>23.86</v>
       </c>
-      <c r="K23" s="5">
+      <c r="K23" s="4">
         <v>0.125</v>
       </c>
-      <c r="L23" s="5">
-        <v>49.043999999999997</v>
-      </c>
-      <c r="M23" s="4" t="s">
+      <c r="L23" s="4">
+        <v>49.044</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1" t="s">
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4" t="s">
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S23" s="7">
@@ -4335,114 +4355,114 @@
         <v>0</v>
       </c>
       <c r="Z23" s="8">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="AA23" s="8">
-        <v>1.3160000000000001</v>
+        <v>1.316</v>
       </c>
       <c r="AB23" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC23" s="8">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AD23" s="8">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AE23" s="8">
-        <v>0.14899999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="AF23" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG23" s="8">
-        <v>5.1999999999999998E-2</v>
+        <v>0.052</v>
       </c>
       <c r="AH23" s="8">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI23" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ23" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AK23" s="8">
         <v>0.104</v>
       </c>
       <c r="AL23" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AM23" s="8">
         <v>0</v>
       </c>
       <c r="AN23" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO23" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP23" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ23" s="8">
-        <v>1.7899999999999999E-2</v>
-      </c>
-      <c r="AR23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS23" s="4" t="s">
+        <v>0.0179</v>
+      </c>
+      <c r="AR23" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS23" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT23" s="4" t="s">
+      <c r="AT23" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4" t="s">
+    <row r="24" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>2193378</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>49660</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="5">
         <v>24.83</v>
       </c>
-      <c r="K24" s="5">
+      <c r="K24" s="4">
         <v>0.1346</v>
       </c>
-      <c r="L24" s="5">
-        <v>62.304000000000002</v>
-      </c>
-      <c r="M24" s="4" t="s">
+      <c r="L24" s="4">
+        <v>62.304</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1" t="s">
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4" t="s">
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S24" s="7"/>
@@ -4453,34 +4473,34 @@
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
       <c r="Z24" s="8">
-        <v>5.8999999999999997E-2</v>
+        <v>0.059</v>
       </c>
       <c r="AA24" s="8">
-        <v>0.35699999999999998</v>
+        <v>0.357</v>
       </c>
       <c r="AB24" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AC24" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AD24" s="8">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AE24" s="8">
-        <v>0.13100000000000001</v>
+        <v>0.131</v>
       </c>
       <c r="AF24" s="8">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AG24" s="8">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AH24" s="8">
         <v>0.01</v>
       </c>
       <c r="AI24" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AJ24" s="8">
         <v>0.03</v>
@@ -4489,78 +4509,78 @@
         <v>0</v>
       </c>
       <c r="AL24" s="8">
-        <v>2.5999999999999999E-3</v>
+        <v>0.0026</v>
       </c>
       <c r="AM24" s="8">
         <v>0</v>
       </c>
       <c r="AN24" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO24" s="8">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AP24" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ24" s="8">
-        <v>6.3E-3</v>
-      </c>
-      <c r="AR24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS24" s="4" t="s">
+        <v>0.0063</v>
+      </c>
+      <c r="AR24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT24" s="4" t="s">
+      <c r="AT24" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4" t="s">
+    <row r="25" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>2187272</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>41900</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="5">
         <v>20.95</v>
       </c>
-      <c r="K25" s="5">
+      <c r="K25" s="4">
         <v>0.1598</v>
       </c>
-      <c r="L25" s="5">
-        <v>47.404000000000003</v>
-      </c>
-      <c r="M25" s="4" t="s">
+      <c r="L25" s="4">
+        <v>47.404</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1" t="s">
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4" t="s">
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S25" s="7"/>
@@ -4571,114 +4591,114 @@
       <c r="X25" s="7"/>
       <c r="Y25" s="7"/>
       <c r="Z25" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AA25" s="8">
-        <v>0.13300000000000001</v>
+        <v>0.133</v>
       </c>
       <c r="AB25" s="8">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AC25" s="8">
-        <v>8.0000000000000004E-4</v>
+        <v>0.0008</v>
       </c>
       <c r="AD25" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AE25" s="8">
-        <v>9.9000000000000005E-2</v>
+        <v>0.099</v>
       </c>
       <c r="AF25" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AG25" s="8">
-        <v>3.6999999999999998E-2</v>
+        <v>0.037</v>
       </c>
       <c r="AH25" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI25" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ25" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK25" s="8">
         <v>0</v>
       </c>
       <c r="AL25" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AM25" s="8">
         <v>0</v>
       </c>
       <c r="AN25" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO25" s="8">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AP25" s="8">
         <v>0</v>
       </c>
       <c r="AQ25" s="8">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="AR25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS25" s="4" t="s">
+        <v>0.0055</v>
+      </c>
+      <c r="AR25" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS25" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT25" s="4" t="s">
+      <c r="AT25" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4" t="s">
+    <row r="26" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>2187274</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>28960</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="5">
         <v>14.48</v>
       </c>
-      <c r="K26" s="5">
-        <v>0.15989999999999999</v>
-      </c>
-      <c r="L26" s="5">
+      <c r="K26" s="4">
+        <v>0.1599</v>
+      </c>
+      <c r="L26" s="4">
         <v>47.48</v>
       </c>
-      <c r="M26" s="4" t="s">
+      <c r="M26" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1" t="s">
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="4" t="s">
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S26" s="7"/>
@@ -4689,114 +4709,114 @@
       <c r="X26" s="7"/>
       <c r="Y26" s="7"/>
       <c r="Z26" s="8">
-        <v>2.5000000000000001E-2</v>
+        <v>0.025</v>
       </c>
       <c r="AA26" s="8">
         <v>0.126</v>
       </c>
       <c r="AB26" s="8">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AC26" s="8">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AD26" s="8">
-        <v>1.7999999999999999E-2</v>
+        <v>0.018</v>
       </c>
       <c r="AE26" s="8">
-        <v>8.1000000000000003E-2</v>
+        <v>0.081</v>
       </c>
       <c r="AF26" s="8">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AG26" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AH26" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI26" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ26" s="8">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="AK26" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AL26" s="8">
-        <v>5.9999999999999995E-4</v>
+        <v>0.0006</v>
       </c>
       <c r="AM26" s="8">
         <v>0</v>
       </c>
       <c r="AN26" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO26" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP26" s="8">
         <v>0</v>
       </c>
       <c r="AQ26" s="8">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="AR26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS26" s="4" t="s">
+        <v>0.0073</v>
+      </c>
+      <c r="AR26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS26" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT26" s="4" t="s">
+      <c r="AT26" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:46" s="3" customFormat="1" ht="127.5" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4" t="s">
+    <row r="27" ht="127.5" customHeight="1" s="1" customFormat="1">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>2196622</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="5">
         <v>48100</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="5">
         <v>24.05</v>
       </c>
-      <c r="K27" s="5">
+      <c r="K27" s="4">
         <v>0.1666</v>
       </c>
-      <c r="L27" s="5">
-        <v>58.658000000000001</v>
-      </c>
-      <c r="M27" s="4" t="s">
+      <c r="L27" s="4">
+        <v>58.658</v>
+      </c>
+      <c r="M27" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1" t="s">
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4" t="s">
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S27" s="7">
@@ -4827,108 +4847,108 @@
         <v>1.107</v>
       </c>
       <c r="AB27" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AC27" s="8">
-        <v>1.5E-3</v>
+        <v>0.0015</v>
       </c>
       <c r="AD27" s="8">
-        <v>0.19400000000000001</v>
+        <v>0.194</v>
       </c>
       <c r="AE27" s="8">
         <v>0.121</v>
       </c>
       <c r="AF27" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AG27" s="8">
-        <v>4.9000000000000002E-2</v>
+        <v>0.049</v>
       </c>
       <c r="AH27" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI27" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ27" s="8">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AK27" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL27" s="8">
-        <v>3.44E-2</v>
+        <v>0.0344</v>
       </c>
       <c r="AM27" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN27" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO27" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AP27" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ27" s="8">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="AR27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS27" s="4" t="s">
+        <v>0.007</v>
+      </c>
+      <c r="AR27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS27" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT27" s="4" t="s">
+      <c r="AT27" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4" t="s">
+    <row r="28" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>2195841</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>48620</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="5">
         <v>24.31</v>
       </c>
-      <c r="K28" s="5">
-        <v>0.18190000000000001</v>
-      </c>
-      <c r="L28" s="5">
-        <v>48.762999999999998</v>
-      </c>
-      <c r="M28" s="4" t="s">
+      <c r="K28" s="4">
+        <v>0.1819</v>
+      </c>
+      <c r="L28" s="4">
+        <v>48.763</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1" t="s">
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="4" t="s">
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S28" s="7"/>
@@ -4939,114 +4959,114 @@
       <c r="X28" s="7"/>
       <c r="Y28" s="7"/>
       <c r="Z28" s="8">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="AA28" s="8">
-        <v>0.34200000000000003</v>
+        <v>0.342</v>
       </c>
       <c r="AB28" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC28" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AD28" s="8">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="AE28" s="8">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="AF28" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AG28" s="8">
-        <v>5.0999999999999997E-2</v>
+        <v>0.051</v>
       </c>
       <c r="AH28" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI28" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ28" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AK28" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL28" s="8">
-        <v>2.8E-3</v>
+        <v>0.0028</v>
       </c>
       <c r="AM28" s="8">
         <v>0</v>
       </c>
       <c r="AN28" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO28" s="8">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AP28" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ28" s="8">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="AR28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS28" s="4" t="s">
+        <v>0.0069</v>
+      </c>
+      <c r="AR28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT28" s="4" t="s">
+      <c r="AT28" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4" t="s">
+    <row r="29" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>2193604</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>47260</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="5">
         <v>23.63</v>
       </c>
-      <c r="K29" s="5">
-        <v>0.18459999999999999</v>
-      </c>
-      <c r="L29" s="5">
-        <v>52.165999999999997</v>
-      </c>
-      <c r="M29" s="4" t="s">
+      <c r="K29" s="4">
+        <v>0.1846</v>
+      </c>
+      <c r="L29" s="4">
+        <v>52.166</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1" t="s">
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4" t="s">
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S29" s="7"/>
@@ -5057,114 +5077,114 @@
       <c r="X29" s="7"/>
       <c r="Y29" s="7"/>
       <c r="Z29" s="8">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="AA29" s="8">
         <v>0.49</v>
       </c>
       <c r="AB29" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC29" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AD29" s="8">
-        <v>1.7000000000000001E-2</v>
+        <v>0.017</v>
       </c>
       <c r="AE29" s="8">
-        <v>9.0999999999999998E-2</v>
+        <v>0.091</v>
       </c>
       <c r="AF29" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG29" s="8">
         <v>0.05</v>
       </c>
       <c r="AH29" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AI29" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ29" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AK29" s="8">
         <v>0</v>
       </c>
       <c r="AL29" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AM29" s="8">
         <v>0</v>
       </c>
       <c r="AN29" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO29" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP29" s="8">
         <v>0</v>
       </c>
       <c r="AQ29" s="8">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="AR29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS29" s="4" t="s">
+        <v>0.0062</v>
+      </c>
+      <c r="AR29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT29" s="4" t="s">
+      <c r="AT29" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4" t="s">
+    <row r="30" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>2190592</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="5">
         <v>35600</v>
       </c>
-      <c r="J30" s="6">
+      <c r="J30" s="5">
         <v>17.8</v>
       </c>
-      <c r="K30" s="5">
-        <v>0.20019999999999999</v>
-      </c>
-      <c r="L30" s="5">
-        <v>48.798999999999999</v>
-      </c>
-      <c r="M30" s="4" t="s">
+      <c r="K30" s="4">
+        <v>0.2002</v>
+      </c>
+      <c r="L30" s="4">
+        <v>48.799</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1" t="s">
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4" t="s">
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S30" s="7">
@@ -5189,114 +5209,114 @@
         <v>0</v>
       </c>
       <c r="Z30" s="8">
-        <v>0.23799999999999999</v>
+        <v>0.238</v>
       </c>
       <c r="AA30" s="8">
         <v>1.27</v>
       </c>
       <c r="AB30" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AC30" s="8">
-        <v>5.9999999999999995E-4</v>
+        <v>0.0006</v>
       </c>
       <c r="AD30" s="8">
         <v>0.188</v>
       </c>
       <c r="AE30" s="8">
-        <v>0.11799999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="AF30" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AG30" s="8">
-        <v>6.6000000000000003E-2</v>
+        <v>0.066</v>
       </c>
       <c r="AH30" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI30" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ30" s="8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.036</v>
       </c>
       <c r="AK30" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL30" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AM30" s="8">
         <v>0</v>
       </c>
       <c r="AN30" s="8">
-        <v>3.0000000000000001E-3</v>
+        <v>0.003</v>
       </c>
       <c r="AO30" s="8">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP30" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ30" s="8">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="AR30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS30" s="4" t="s">
+        <v>0.0064</v>
+      </c>
+      <c r="AR30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS30" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT30" s="4" t="s">
+      <c r="AT30" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4" t="s">
+    <row r="31" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>2196787</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="5">
         <v>38020</v>
       </c>
-      <c r="J31" s="6">
-        <v>19.010000000000002</v>
-      </c>
-      <c r="K31" s="5">
+      <c r="J31" s="5">
+        <v>19.01</v>
+      </c>
+      <c r="K31" s="4">
         <v>0.2248</v>
       </c>
-      <c r="L31" s="5">
-        <v>52.151000000000003</v>
-      </c>
-      <c r="M31" s="4" t="s">
+      <c r="L31" s="4">
+        <v>52.151</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1" t="s">
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4" t="s">
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S31" s="7">
@@ -5321,16 +5341,16 @@
         <v>28</v>
       </c>
       <c r="Z31" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AA31" s="8">
         <v>1.321</v>
       </c>
       <c r="AB31" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC31" s="8">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AD31" s="8">
         <v>0.182</v>
@@ -5339,98 +5359,98 @@
         <v>0.113</v>
       </c>
       <c r="AF31" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG31" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH31" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI31" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ31" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AK31" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AL31" s="8">
-        <v>4.2799999999999998E-2</v>
+        <v>0.0428</v>
       </c>
       <c r="AM31" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN31" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO31" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP31" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ31" s="8">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="AR31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS31" s="4" t="s">
+        <v>0.0068</v>
+      </c>
+      <c r="AR31" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT31" s="4" t="s">
+      <c r="AT31" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4" t="s">
+    <row r="32" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>2198321</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <v>58000</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="5">
         <v>29</v>
       </c>
-      <c r="K32" s="5">
-        <v>0.22489999999999999</v>
-      </c>
-      <c r="L32" s="5">
-        <v>59.347999999999999</v>
-      </c>
-      <c r="M32" s="4" t="s">
+      <c r="K32" s="4">
+        <v>0.2249</v>
+      </c>
+      <c r="L32" s="4">
+        <v>59.348</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1" t="s">
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="Q32" s="4" t="s">
+      <c r="Q32" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="R32" s="4" t="s">
+      <c r="R32" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S32" s="7"/>
@@ -5441,16 +5461,16 @@
       <c r="X32" s="7"/>
       <c r="Y32" s="7"/>
       <c r="Z32" s="8">
-        <v>0.20699999999999999</v>
+        <v>0.207</v>
       </c>
       <c r="AA32" s="8">
         <v>0.78</v>
       </c>
       <c r="AB32" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC32" s="8">
-        <v>5.9999999999999995E-4</v>
+        <v>0.0006</v>
       </c>
       <c r="AD32" s="8">
         <v>0.03</v>
@@ -5459,96 +5479,96 @@
         <v>0.114</v>
       </c>
       <c r="AF32" s="8">
-        <v>3.4000000000000002E-2</v>
+        <v>0.034</v>
       </c>
       <c r="AG32" s="8">
         <v>0.05</v>
       </c>
       <c r="AH32" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI32" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ32" s="8">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AK32" s="8">
         <v>0</v>
       </c>
       <c r="AL32" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AM32" s="8">
         <v>0</v>
       </c>
       <c r="AN32" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO32" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP32" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ32" s="8">
-        <v>7.4000000000000003E-3</v>
-      </c>
-      <c r="AR32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS32" s="4" t="s">
+        <v>0.0074</v>
+      </c>
+      <c r="AR32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS32" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT32" s="4" t="s">
+      <c r="AT32" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
+    <row r="33" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>2196716</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>46700</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="5">
         <v>23.35</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="4">
         <v>0.2301</v>
       </c>
-      <c r="L33" s="5">
-        <v>56.420999999999999</v>
-      </c>
-      <c r="M33" s="4" t="s">
+      <c r="L33" s="4">
+        <v>56.421</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="1" t="s">
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4" t="s">
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S33" s="7"/>
@@ -5559,114 +5579,114 @@
       <c r="X33" s="7"/>
       <c r="Y33" s="7"/>
       <c r="Z33" s="8">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AA33" s="8">
-        <v>0.59399999999999997</v>
+        <v>0.594</v>
       </c>
       <c r="AB33" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC33" s="8">
-        <v>2.0999999999999999E-3</v>
+        <v>0.0021</v>
       </c>
       <c r="AD33" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AE33" s="8">
-        <v>8.4000000000000005E-2</v>
+        <v>0.084</v>
       </c>
       <c r="AF33" s="8">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG33" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AH33" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI33" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ33" s="8">
-        <v>2.5999999999999999E-2</v>
+        <v>0.026</v>
       </c>
       <c r="AK33" s="8">
         <v>0</v>
       </c>
       <c r="AL33" s="8">
-        <v>2.63E-2</v>
+        <v>0.0263</v>
       </c>
       <c r="AM33" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN33" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO33" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP33" s="8">
         <v>0</v>
       </c>
       <c r="AQ33" s="8">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="AR33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS33" s="4" t="s">
+        <v>0.0069</v>
+      </c>
+      <c r="AR33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS33" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT33" s="4" t="s">
+      <c r="AT33" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4" t="s">
+    <row r="34" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>2196725</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>43060</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <v>21.53</v>
       </c>
-      <c r="K34" s="5">
-        <v>0.24679999999999999</v>
-      </c>
-      <c r="L34" s="5">
+      <c r="K34" s="4">
+        <v>0.2468</v>
+      </c>
+      <c r="L34" s="4">
         <v>51.86</v>
       </c>
-      <c r="M34" s="4" t="s">
+      <c r="M34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="1" t="s">
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4" t="s">
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S34" s="7"/>
@@ -5677,114 +5697,114 @@
       <c r="X34" s="7"/>
       <c r="Y34" s="7"/>
       <c r="Z34" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AA34" s="8">
         <v>1.343</v>
       </c>
       <c r="AB34" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC34" s="8">
-        <v>1.6000000000000001E-3</v>
+        <v>0.0016</v>
       </c>
       <c r="AD34" s="8">
-        <v>0.18099999999999999</v>
+        <v>0.181</v>
       </c>
       <c r="AE34" s="8">
-        <v>9.8000000000000004E-2</v>
+        <v>0.098</v>
       </c>
       <c r="AF34" s="8">
         <v>0.03</v>
       </c>
       <c r="AG34" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH34" s="8">
         <v>0.01</v>
       </c>
       <c r="AI34" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ34" s="8">
         <v>0.03</v>
       </c>
       <c r="AK34" s="8">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AL34" s="8">
-        <v>4.19E-2</v>
+        <v>0.0419</v>
       </c>
       <c r="AM34" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN34" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO34" s="8">
-        <v>2.2000000000000001E-3</v>
+        <v>0.0022</v>
       </c>
       <c r="AP34" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ34" s="8">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="AR34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS34" s="4" t="s">
+        <v>0.0069</v>
+      </c>
+      <c r="AR34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS34" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT34" s="4" t="s">
+      <c r="AT34" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:46" s="3" customFormat="1" ht="73.5" customHeight="1">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4" t="s">
+    <row r="35" ht="73.5" customHeight="1" s="1" customFormat="1">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>2193430</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>43980</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="5">
         <v>21.99</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="4">
         <v>0.2485</v>
       </c>
-      <c r="L35" s="5">
-        <v>61.856999999999999</v>
-      </c>
-      <c r="M35" s="4" t="s">
+      <c r="L35" s="4">
+        <v>61.857</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="1" t="s">
+      <c r="N35" s="3"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4" t="s">
+      <c r="Q35" s="3"/>
+      <c r="R35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S35" s="7"/>
@@ -5795,114 +5815,114 @@
       <c r="X35" s="7"/>
       <c r="Y35" s="7"/>
       <c r="Z35" s="8">
-        <v>6.5000000000000002E-2</v>
+        <v>0.065</v>
       </c>
       <c r="AA35" s="8">
-        <v>0.47099999999999997</v>
+        <v>0.471</v>
       </c>
       <c r="AB35" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC35" s="8">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AD35" s="8">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="AE35" s="8">
-        <v>8.2000000000000003E-2</v>
+        <v>0.082</v>
       </c>
       <c r="AF35" s="8">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AG35" s="8">
         <v>0.05</v>
       </c>
       <c r="AH35" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI35" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AJ35" s="8">
         <v>0.03</v>
       </c>
       <c r="AK35" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL35" s="8">
-        <v>3.8E-3</v>
+        <v>0.0038</v>
       </c>
       <c r="AM35" s="8">
         <v>0</v>
       </c>
       <c r="AN35" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO35" s="8">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AP35" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ35" s="8">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="AR35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS35" s="4" t="s">
+        <v>0.0062</v>
+      </c>
+      <c r="AR35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS35" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT35" s="4" t="s">
+      <c r="AT35" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:46" s="3" customFormat="1" ht="106.15" customHeight="1">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4" t="s">
+    <row r="36" ht="106.5" customHeight="1" s="1" customFormat="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>2194021</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="5">
         <v>55500</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="5">
         <v>27.75</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="4">
         <v>0.2492</v>
       </c>
-      <c r="L36" s="5">
+      <c r="L36" s="4">
         <v>60.37</v>
       </c>
-      <c r="M36" s="4" t="s">
+      <c r="M36" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="1" t="s">
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4" t="s">
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S36" s="7">
@@ -5930,113 +5950,113 @@
         <v>0.05</v>
       </c>
       <c r="AA36" s="8">
-        <v>0.56000000000000005</v>
+        <v>0.56</v>
       </c>
       <c r="AB36" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC36" s="8">
-        <v>3.8999999999999998E-3</v>
+        <v>0.0039</v>
       </c>
       <c r="AD36" s="8">
-        <v>8.0000000000000002E-3</v>
+        <v>0.008</v>
       </c>
       <c r="AE36" s="8">
-        <v>8.6999999999999994E-2</v>
+        <v>0.087</v>
       </c>
       <c r="AF36" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AG36" s="8">
-        <v>4.4999999999999998E-2</v>
+        <v>0.045</v>
       </c>
       <c r="AH36" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI36" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ36" s="8">
-        <v>2.3E-2</v>
+        <v>0.023</v>
       </c>
       <c r="AK36" s="8">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="AL36" s="8">
-        <v>4.0000000000000002E-4</v>
+        <v>0.0004</v>
       </c>
       <c r="AM36" s="8">
         <v>0</v>
       </c>
       <c r="AN36" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AO36" s="8">
-        <v>1.2999999999999999E-3</v>
+        <v>0.0013</v>
       </c>
       <c r="AP36" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ36" s="8">
-        <v>1.3299999999999999E-2</v>
-      </c>
-      <c r="AR36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS36" s="4" t="s">
+        <v>0.0133</v>
+      </c>
+      <c r="AR36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS36" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT36" s="4" t="s">
+      <c r="AT36" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:46" s="3" customFormat="1" ht="170.65" customHeight="1">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4" t="s">
+    <row r="37" ht="171" customHeight="1" s="1" customFormat="1">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <v>2188053</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="5">
         <v>52060</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="5">
         <v>26.03</v>
       </c>
-      <c r="K37" s="5">
-        <v>0.26490000000000002</v>
-      </c>
-      <c r="L37" s="5">
-        <v>51.816000000000003</v>
-      </c>
-      <c r="M37" s="4" t="s">
+      <c r="K37" s="4">
+        <v>0.2649</v>
+      </c>
+      <c r="L37" s="4">
+        <v>51.816</v>
+      </c>
+      <c r="M37" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="1" t="s">
+      <c r="N37" s="3"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="Q37" s="4" t="s">
+      <c r="Q37" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="R37" s="4" t="s">
+      <c r="R37" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S37" s="7">
@@ -6061,19 +6081,19 @@
         <v>31</v>
       </c>
       <c r="Z37" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AA37" s="8">
         <v>1.306</v>
       </c>
       <c r="AB37" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC37" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AD37" s="8">
-        <v>0.17100000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="AE37" s="8">
         <v>0.104</v>
@@ -6082,93 +6102,93 @@
         <v>0.04</v>
       </c>
       <c r="AG37" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AH37" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI37" s="8">
-        <v>6.0000000000000001E-3</v>
+        <v>0.006</v>
       </c>
       <c r="AJ37" s="8">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AK37" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AL37" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AM37" s="8">
         <v>0</v>
       </c>
       <c r="AN37" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO37" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP37" s="8">
         <v>0</v>
       </c>
       <c r="AQ37" s="8">
-        <v>6.3E-3</v>
-      </c>
-      <c r="AR37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS37" s="4" t="s">
+        <v>0.0063</v>
+      </c>
+      <c r="AR37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS37" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT37" s="4" t="s">
+      <c r="AT37" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="38" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4" t="s">
+    <row r="38" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>2189966</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G38" s="4" t="s">
+      <c r="G38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="5">
         <v>26380</v>
       </c>
-      <c r="J38" s="6">
+      <c r="J38" s="5">
         <v>13.19</v>
       </c>
-      <c r="K38" s="5">
-        <v>0.30630000000000002</v>
-      </c>
-      <c r="L38" s="5">
-        <v>51.884999999999998</v>
-      </c>
-      <c r="M38" s="4" t="s">
+      <c r="K38" s="4">
+        <v>0.3063</v>
+      </c>
+      <c r="L38" s="4">
+        <v>51.885</v>
+      </c>
+      <c r="M38" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="1" t="s">
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4" t="s">
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S38" s="7"/>
@@ -6182,113 +6202,113 @@
         <v>0.04</v>
       </c>
       <c r="AA38" s="8">
-        <v>1.1220000000000001</v>
+        <v>1.122</v>
       </c>
       <c r="AB38" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC38" s="8">
-        <v>1.1000000000000001E-3</v>
+        <v>0.0011</v>
       </c>
       <c r="AD38" s="8">
         <v>0.183</v>
       </c>
       <c r="AE38" s="8">
-        <v>8.7999999999999995E-2</v>
+        <v>0.088</v>
       </c>
       <c r="AF38" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG38" s="8">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH38" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI38" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ38" s="8">
-        <v>3.3000000000000002E-2</v>
+        <v>0.033</v>
       </c>
       <c r="AK38" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL38" s="8">
-        <v>4.24E-2</v>
+        <v>0.0424</v>
       </c>
       <c r="AM38" s="8">
         <v>0</v>
       </c>
       <c r="AN38" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AO38" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP38" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ38" s="8">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="AR38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS38" s="4" t="s">
+        <v>0.0068</v>
+      </c>
+      <c r="AR38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS38" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT38" s="4" t="s">
+      <c r="AT38" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4" t="s">
+    <row r="39" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="4">
         <v>2196788</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="5">
         <v>51820</v>
       </c>
-      <c r="J39" s="6">
+      <c r="J39" s="5">
         <v>25.91</v>
       </c>
-      <c r="K39" s="5">
-        <v>0.30719999999999997</v>
-      </c>
-      <c r="L39" s="5">
-        <v>52.104999999999997</v>
-      </c>
-      <c r="M39" s="4" t="s">
+      <c r="K39" s="4">
+        <v>0.3072</v>
+      </c>
+      <c r="L39" s="4">
+        <v>52.105</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="1" t="s">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3"/>
+      <c r="P39" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="Q39" s="4" t="s">
+      <c r="Q39" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="R39" s="4" t="s">
+      <c r="R39" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S39" s="7">
@@ -6304,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="W39" s="7">
-        <v>73.510000000000005</v>
+        <v>73.51</v>
       </c>
       <c r="X39" s="7">
         <v>86.57</v>
@@ -6313,16 +6333,16 @@
         <v>29.15</v>
       </c>
       <c r="Z39" s="8">
-        <v>4.2000000000000003E-2</v>
+        <v>0.042</v>
       </c>
       <c r="AA39" s="8">
         <v>1.321</v>
       </c>
       <c r="AB39" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC39" s="8">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AD39" s="8">
         <v>0.182</v>
@@ -6331,96 +6351,96 @@
         <v>0.113</v>
       </c>
       <c r="AF39" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG39" s="8">
-        <v>4.7E-2</v>
+        <v>0.047</v>
       </c>
       <c r="AH39" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI39" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ39" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AK39" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AL39" s="8">
-        <v>4.2799999999999998E-2</v>
+        <v>0.0428</v>
       </c>
       <c r="AM39" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN39" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO39" s="8">
-        <v>2.3E-3</v>
+        <v>0.0023</v>
       </c>
       <c r="AP39" s="8">
-        <v>2.0000000000000001E-4</v>
+        <v>0.0002</v>
       </c>
       <c r="AQ39" s="8">
-        <v>6.7999999999999996E-3</v>
-      </c>
-      <c r="AR39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS39" s="4" t="s">
+        <v>0.0068</v>
+      </c>
+      <c r="AR39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS39" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT39" s="4" t="s">
+      <c r="AT39" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:46" s="3" customFormat="1" ht="62.85" customHeight="1">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4" t="s">
+    <row r="40" ht="63" customHeight="1" s="1" customFormat="1">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="4">
         <v>2196948</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>28540</v>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="5">
         <v>14.27</v>
       </c>
-      <c r="K40" s="5">
-        <v>0.34960000000000002</v>
-      </c>
-      <c r="L40" s="5">
-        <v>51.825000000000003</v>
-      </c>
-      <c r="M40" s="4" t="s">
+      <c r="K40" s="4">
+        <v>0.3496</v>
+      </c>
+      <c r="L40" s="4">
+        <v>51.825</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="1" t="s">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4" t="s">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S40" s="7"/>
@@ -6431,114 +6451,114 @@
       <c r="X40" s="7"/>
       <c r="Y40" s="7"/>
       <c r="Z40" s="8">
-        <v>4.1000000000000002E-2</v>
+        <v>0.041</v>
       </c>
       <c r="AA40" s="8">
         <v>1.157</v>
       </c>
       <c r="AB40" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC40" s="8">
-        <v>8.9999999999999998E-4</v>
+        <v>0.0009</v>
       </c>
       <c r="AD40" s="8">
-        <v>0.19800000000000001</v>
+        <v>0.198</v>
       </c>
       <c r="AE40" s="8">
         <v>0.124</v>
       </c>
       <c r="AF40" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AG40" s="8">
-        <v>5.5E-2</v>
+        <v>0.055</v>
       </c>
       <c r="AH40" s="8">
         <v>0.01</v>
       </c>
       <c r="AI40" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ40" s="8">
-        <v>3.2000000000000001E-2</v>
+        <v>0.032</v>
       </c>
       <c r="AK40" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL40" s="8">
-        <v>4.2799999999999998E-2</v>
+        <v>0.0428</v>
       </c>
       <c r="AM40" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN40" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AO40" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AP40" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ40" s="8">
-        <v>7.1000000000000004E-3</v>
-      </c>
-      <c r="AR40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS40" s="4" t="s">
+        <v>0.0071</v>
+      </c>
+      <c r="AR40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS40" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT40" s="4" t="s">
+      <c r="AT40" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4" t="s">
+    <row r="41" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>2196852</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="5">
         <v>43900</v>
       </c>
-      <c r="J41" s="6">
+      <c r="J41" s="5">
         <v>21.95</v>
       </c>
-      <c r="K41" s="5">
-        <v>0.36720000000000003</v>
-      </c>
-      <c r="L41" s="5">
-        <v>51.597999999999999</v>
-      </c>
-      <c r="M41" s="4" t="s">
+      <c r="K41" s="4">
+        <v>0.3672</v>
+      </c>
+      <c r="L41" s="4">
+        <v>51.598</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="1" t="s">
+      <c r="N41" s="3"/>
+      <c r="O41" s="3"/>
+      <c r="P41" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4" t="s">
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S41" s="7"/>
@@ -6549,123 +6569,123 @@
       <c r="X41" s="7"/>
       <c r="Y41" s="7"/>
       <c r="Z41" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AA41" s="8">
-        <v>1.1020000000000001</v>
+        <v>1.102</v>
       </c>
       <c r="AB41" s="8">
-        <v>1.2999999999999999E-2</v>
+        <v>0.013</v>
       </c>
       <c r="AC41" s="8">
-        <v>2.3999999999999998E-3</v>
+        <v>0.0024</v>
       </c>
       <c r="AD41" s="8">
-        <v>0.17199999999999999</v>
+        <v>0.172</v>
       </c>
       <c r="AE41" s="8">
-        <v>0.14299999999999999</v>
+        <v>0.143</v>
       </c>
       <c r="AF41" s="8">
-        <v>3.9E-2</v>
+        <v>0.039</v>
       </c>
       <c r="AG41" s="8">
-        <v>4.8000000000000001E-2</v>
+        <v>0.048</v>
       </c>
       <c r="AH41" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AI41" s="8">
-        <v>5.0000000000000001E-3</v>
+        <v>0.005</v>
       </c>
       <c r="AJ41" s="8">
-        <v>3.1E-2</v>
+        <v>0.031</v>
       </c>
       <c r="AK41" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AL41" s="8">
-        <v>4.3099999999999999E-2</v>
+        <v>0.0431</v>
       </c>
       <c r="AM41" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN41" s="8">
-        <v>1.2E-2</v>
+        <v>0.012</v>
       </c>
       <c r="AO41" s="8">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP41" s="8">
         <v>0</v>
       </c>
       <c r="AQ41" s="8">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="AR41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS41" s="4" t="s">
+        <v>0.0065</v>
+      </c>
+      <c r="AR41" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS41" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT41" s="4" t="s">
+      <c r="AT41" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4" t="s">
+    <row r="42" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>2187637</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>41340</v>
       </c>
-      <c r="J42" s="6">
+      <c r="J42" s="5">
         <v>20.67</v>
       </c>
-      <c r="K42" s="5">
-        <v>7.85E-2</v>
-      </c>
-      <c r="L42" s="5">
-        <v>53.422600000000003</v>
-      </c>
-      <c r="M42" s="4" t="s">
+      <c r="K42" s="4">
+        <v>0.0785</v>
+      </c>
+      <c r="L42" s="4">
+        <v>53.4226</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4" t="s">
+      <c r="N42" s="3"/>
+      <c r="O42" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="P42" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4" t="s">
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3" t="s">
         <v>56</v>
       </c>
       <c r="S42" s="7">
-        <v>70.400000000000006</v>
+        <v>70.4</v>
       </c>
       <c r="T42" s="7">
-        <v>81.900000000000006</v>
+        <v>81.9</v>
       </c>
       <c r="U42" s="7">
         <v>24</v>
@@ -6683,122 +6703,122 @@
         <v>0</v>
       </c>
       <c r="Z42" s="8">
-        <v>4.5999999999999999E-2</v>
+        <v>0.046</v>
       </c>
       <c r="AA42" s="8">
-        <v>0.55600000000000005</v>
+        <v>0.556</v>
       </c>
       <c r="AB42" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AC42" s="8">
-        <v>6.9999999999999999E-4</v>
+        <v>0.0007</v>
       </c>
       <c r="AD42" s="8">
-        <v>1.4999999999999999E-2</v>
+        <v>0.015</v>
       </c>
       <c r="AE42" s="8">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="AF42" s="8">
-        <v>2.9000000000000001E-2</v>
+        <v>0.029</v>
       </c>
       <c r="AG42" s="8">
-        <v>3.7999999999999999E-2</v>
+        <v>0.038</v>
       </c>
       <c r="AH42" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI42" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ42" s="8">
-        <v>2.8000000000000001E-2</v>
+        <v>0.028</v>
       </c>
       <c r="AK42" s="8">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="AL42" s="8">
-        <v>2.7000000000000001E-3</v>
+        <v>0.0027</v>
       </c>
       <c r="AM42" s="8">
         <v>0</v>
       </c>
       <c r="AN42" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO42" s="8">
-        <v>2.5000000000000001E-3</v>
+        <v>0.0025</v>
       </c>
       <c r="AP42" s="8">
         <v>0</v>
       </c>
       <c r="AQ42" s="8">
-        <v>1.5699999999999999E-2</v>
-      </c>
-      <c r="AR42" s="4" t="s">
+        <v>0.0157</v>
+      </c>
+      <c r="AR42" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AS42" s="4" t="s">
+      <c r="AS42" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT42" s="4" t="s">
+      <c r="AT42" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:46" s="3" customFormat="1" ht="94.9" customHeight="1">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4" t="s">
+    <row r="43" ht="95.25" customHeight="1" s="1" customFormat="1">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="4">
         <v>2195702.1</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="5">
         <v>41575</v>
       </c>
-      <c r="J43" s="6">
-        <v>20.787500000000001</v>
-      </c>
-      <c r="K43" s="5">
-        <v>7.9200000000000007E-2</v>
-      </c>
-      <c r="L43" s="5">
-        <v>44.845999999999997</v>
-      </c>
-      <c r="M43" s="4" t="s">
+      <c r="J43" s="5">
+        <v>20.7875</v>
+      </c>
+      <c r="K43" s="4">
+        <v>0.0792</v>
+      </c>
+      <c r="L43" s="4">
+        <v>44.846</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4" t="s">
+      <c r="N43" s="3"/>
+      <c r="O43" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P43" s="1" t="s">
+      <c r="P43" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="Q43" s="4" t="s">
+      <c r="Q43" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="R43" s="4" t="s">
+      <c r="R43" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S43" s="7">
-        <v>80.599999999999994</v>
+        <v>80.6</v>
       </c>
       <c r="T43" s="7">
         <v>89.8</v>
@@ -6819,118 +6839,118 @@
         <v>0</v>
       </c>
       <c r="Z43" s="8">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="AA43" s="8">
-        <v>1.2669999999999999</v>
+        <v>1.267</v>
       </c>
       <c r="AB43" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC43" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD43" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AE43" s="8">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF43" s="8">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AG43" s="8">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="AH43" s="8">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI43" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ43" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK43" s="8">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AL43" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AM43" s="8">
         <v>0</v>
       </c>
       <c r="AN43" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO43" s="8">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP43" s="8">
         <v>0</v>
       </c>
       <c r="AQ43" s="8">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="AR43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS43" s="4" t="s">
+        <v>0.0175</v>
+      </c>
+      <c r="AR43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS43" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT43" s="4" t="s">
+      <c r="AT43" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4" t="s">
+    <row r="44" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>2195704.1</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="5">
         <v>19160</v>
       </c>
-      <c r="J44" s="6">
+      <c r="J44" s="5">
         <v>9.58</v>
       </c>
-      <c r="K44" s="5">
-        <v>7.9299999999999995E-2</v>
-      </c>
-      <c r="L44" s="5">
-        <v>44.835999999999999</v>
-      </c>
-      <c r="M44" s="4" t="s">
+      <c r="K44" s="4">
+        <v>0.0793</v>
+      </c>
+      <c r="L44" s="4">
+        <v>44.836</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4" t="s">
+      <c r="N44" s="3"/>
+      <c r="O44" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="P44" s="1" t="s">
+      <c r="P44" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="Q44" s="4" t="s">
+      <c r="Q44" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="R44" s="4" t="s">
+      <c r="R44" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S44" s="7">
@@ -6955,125 +6975,125 @@
         <v>0</v>
       </c>
       <c r="Z44" s="8">
-        <v>5.2999999999999999E-2</v>
+        <v>0.053</v>
       </c>
       <c r="AA44" s="8">
-        <v>1.2669999999999999</v>
+        <v>1.267</v>
       </c>
       <c r="AB44" s="8">
-        <v>1.4E-2</v>
+        <v>0.014</v>
       </c>
       <c r="AC44" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AD44" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AE44" s="8">
-        <v>8.5999999999999993E-2</v>
+        <v>0.086</v>
       </c>
       <c r="AF44" s="8">
-        <v>2.7E-2</v>
+        <v>0.027</v>
       </c>
       <c r="AG44" s="8">
-        <v>4.2999999999999997E-2</v>
+        <v>0.043</v>
       </c>
       <c r="AH44" s="8">
-        <v>7.0000000000000001E-3</v>
+        <v>0.007</v>
       </c>
       <c r="AI44" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ44" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK44" s="8">
-        <v>0.10199999999999999</v>
+        <v>0.102</v>
       </c>
       <c r="AL44" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AM44" s="8">
         <v>0</v>
       </c>
       <c r="AN44" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO44" s="8">
-        <v>1.9E-3</v>
+        <v>0.0019</v>
       </c>
       <c r="AP44" s="8">
         <v>0</v>
       </c>
       <c r="AQ44" s="8">
-        <v>1.7500000000000002E-2</v>
-      </c>
-      <c r="AR44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS44" s="4" t="s">
+        <v>0.0175</v>
+      </c>
+      <c r="AR44" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS44" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT44" s="4" t="s">
+      <c r="AT44" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:46" s="3" customFormat="1" ht="84.2" customHeight="1">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4" t="s">
+    <row r="45" ht="84" customHeight="1" s="1" customFormat="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="4">
         <v>2190468</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="F45" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="5">
         <v>48165</v>
       </c>
-      <c r="J45" s="6">
+      <c r="J45" s="5">
         <v>24.0825</v>
       </c>
-      <c r="K45" s="5">
-        <v>0.14760000000000001</v>
-      </c>
-      <c r="L45" s="5">
+      <c r="K45" s="4">
+        <v>0.1476</v>
+      </c>
+      <c r="L45" s="4">
         <v>50.695</v>
       </c>
-      <c r="M45" s="4" t="s">
+      <c r="M45" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4" t="s">
+      <c r="N45" s="3"/>
+      <c r="O45" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="P45" s="1" t="s">
+      <c r="P45" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="Q45" s="4" t="s">
+      <c r="Q45" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="R45" s="4" t="s">
+      <c r="R45" s="3" t="s">
         <v>93</v>
       </c>
       <c r="S45" s="7">
         <v>49.9</v>
       </c>
       <c r="T45" s="7">
-        <v>72.099999999999994</v>
+        <v>72.1</v>
       </c>
       <c r="U45" s="7">
         <v>30</v>
@@ -7094,280 +7114,72 @@
         <v>0.191</v>
       </c>
       <c r="AA45" s="8">
-        <v>0.66200000000000003</v>
+        <v>0.662</v>
       </c>
       <c r="AB45" s="8">
-        <v>1.0999999999999999E-2</v>
+        <v>0.011</v>
       </c>
       <c r="AC45" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AD45" s="8">
-        <v>2.1999999999999999E-2</v>
+        <v>0.022</v>
       </c>
       <c r="AE45" s="8">
-        <v>9.7000000000000003E-2</v>
+        <v>0.097</v>
       </c>
       <c r="AF45" s="8">
         <v>0.03</v>
       </c>
       <c r="AG45" s="8">
-        <v>5.6000000000000001E-2</v>
+        <v>0.056</v>
       </c>
       <c r="AH45" s="8">
-        <v>8.9999999999999993E-3</v>
+        <v>0.009</v>
       </c>
       <c r="AI45" s="8">
-        <v>4.0000000000000001E-3</v>
+        <v>0.004</v>
       </c>
       <c r="AJ45" s="8">
-        <v>3.5000000000000003E-2</v>
+        <v>0.035</v>
       </c>
       <c r="AK45" s="8">
         <v>0</v>
       </c>
       <c r="AL45" s="8">
-        <v>1.8E-3</v>
+        <v>0.0018</v>
       </c>
       <c r="AM45" s="8">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="AN45" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AO45" s="8">
-        <v>2E-3</v>
+        <v>0.002</v>
       </c>
       <c r="AP45" s="8">
-        <v>1E-4</v>
+        <v>0.0001</v>
       </c>
       <c r="AQ45" s="8">
-        <v>6.4999999999999997E-3</v>
-      </c>
-      <c r="AR45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="AS45" s="4" t="s">
+        <v>0.0065</v>
+      </c>
+      <c r="AR45" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AS45" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="AT45" s="4" t="s">
+      <c r="AT45" s="3" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AT45"/>
+  <printOptions/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" pageOrder="downThenOver" orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
+  <extLst/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Kind xmlns="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006A996401455D8D44A169477D654C54DD" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="427b0f0dcc80dd9a75fb73223d41b403">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de5e64243c8b017c27e62ae610adbab9" ns2:_="">
-    <xsd:import namespace="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:Kind" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9bec7cd-2720-47d0-aa86-3e2bb6bfde65" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Kind" ma:index="15" nillable="true" ma:displayName="Kind" ma:internalName="Kind">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ec2506c3-735d-4e70-aa79-204d06275b9f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3ADCC4FD-E2E7-4244-9719-CDF95838A1D1}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{182AA494-E41E-46C2-921D-C18AE7313307}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA2DBFF9-B75A-4A7F-BE39-C1E6E7ADC0F9}"/>
 </file>